--- a/artfynd/A 8412-2024 artfynd.xlsx
+++ b/artfynd/A 8412-2024 artfynd.xlsx
@@ -1431,10 +1431,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120552065</v>
+        <v>121061682</v>
       </c>
       <c r="B9" t="n">
-        <v>91378</v>
+        <v>79679</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,32 +1447,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>757</v>
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grodtjärnsberget, Grodtjärnsberget, Ång</t>
+          <t>Grodtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>625396</v>
+        <v>625371</v>
       </c>
       <c r="R9" t="n">
-        <v>6955526</v>
+        <v>6955482</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1496,12 +1504,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1510,6 +1518,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1528,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121061682</v>
+        <v>120552065</v>
       </c>
       <c r="B10" t="n">
-        <v>79679</v>
+        <v>91378</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,40 +1553,32 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Grodtjärnsberget, Ång</t>
+          <t>Grodtjärnsberget, Grodtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>625371</v>
+        <v>625396</v>
       </c>
       <c r="R10" t="n">
-        <v>6955482</v>
+        <v>6955526</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1601,12 +1602,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1615,7 +1616,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8412-2024 artfynd.xlsx
+++ b/artfynd/A 8412-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121061679</v>
+        <v>121061671</v>
       </c>
       <c r="B2" t="n">
-        <v>79552</v>
+        <v>79555</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>625350</v>
+        <v>625356</v>
       </c>
       <c r="R2" t="n">
-        <v>6955478</v>
+        <v>6955527</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121061647</v>
+        <v>121061682</v>
       </c>
       <c r="B3" t="n">
-        <v>98071</v>
+        <v>79682</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,31 +793,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>625356</v>
+        <v>625371</v>
       </c>
       <c r="R3" t="n">
-        <v>6955527</v>
+        <v>6955482</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120550720</v>
+        <v>121061645</v>
       </c>
       <c r="B4" t="n">
-        <v>79552</v>
+        <v>79549</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,16 +903,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -922,19 +921,22 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grodtjärnsberget, Grodtjärnsberget, Ång</t>
+          <t>Grodtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>625345</v>
+        <v>625356</v>
       </c>
       <c r="R4" t="n">
-        <v>6955540</v>
+        <v>6955527</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -958,27 +960,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:20</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Tidigare känt fynd.</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,6 +974,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1005,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121061683</v>
+        <v>120550720</v>
       </c>
       <c r="B5" t="n">
-        <v>98071</v>
+        <v>79555</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,41 +1009,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>392</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Grodtjärnsberget, Ång</t>
+          <t>Grodtjärnsberget, Grodtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>625374</v>
+        <v>625345</v>
       </c>
       <c r="R5" t="n">
-        <v>6955549</v>
+        <v>6955540</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,17 +1063,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Uppskattningsvis 6-700 bladrosetter</t>
+          <t>Tidigare känt fynd.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1092,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1117,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121061645</v>
+        <v>121061679</v>
       </c>
       <c r="B6" t="n">
-        <v>79546</v>
+        <v>79555</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,16 +1126,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1160,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>625356</v>
+        <v>625350</v>
       </c>
       <c r="R6" t="n">
-        <v>6955527</v>
+        <v>6955478</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,7 +1219,7 @@
         <v>120551674</v>
       </c>
       <c r="B7" t="n">
-        <v>79552</v>
+        <v>79555</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1325,10 +1318,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121061671</v>
+        <v>120552065</v>
       </c>
       <c r="B8" t="n">
-        <v>79552</v>
+        <v>91388</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,44 +1330,36 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>392</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Aspgelélav</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grodtjärnsberget, Ång</t>
+          <t>Grodtjärnsberget, Grodtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>625356</v>
+        <v>625396</v>
       </c>
       <c r="R8" t="n">
-        <v>6955527</v>
+        <v>6955526</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1398,12 +1383,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1412,7 +1397,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1431,10 +1415,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121061682</v>
+        <v>121061647</v>
       </c>
       <c r="B9" t="n">
-        <v>79679</v>
+        <v>98081</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,30 +1427,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1474,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>625371</v>
+        <v>625356</v>
       </c>
       <c r="R9" t="n">
-        <v>6955482</v>
+        <v>6955527</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,10 +1522,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120552065</v>
+        <v>121061683</v>
       </c>
       <c r="B10" t="n">
-        <v>91378</v>
+        <v>98081</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,36 +1534,45 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>757</v>
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Grodtjärnsberget, Grodtjärnsberget, Ång</t>
+          <t>Grodtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>625396</v>
+        <v>625374</v>
       </c>
       <c r="R10" t="n">
-        <v>6955526</v>
+        <v>6955549</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1602,12 +1596,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Uppskattningsvis 6-700 bladrosetter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1616,6 +1615,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8412-2024 artfynd.xlsx
+++ b/artfynd/A 8412-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121061671</v>
+        <v>121061647</v>
       </c>
       <c r="B2" t="n">
-        <v>79555</v>
+        <v>98081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>392</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -781,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121061682</v>
+        <v>121061679</v>
       </c>
       <c r="B3" t="n">
-        <v>79682</v>
+        <v>79555</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>392</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>625371</v>
+        <v>625350</v>
       </c>
       <c r="R3" t="n">
-        <v>6955482</v>
+        <v>6955478</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121061645</v>
+        <v>121061671</v>
       </c>
       <c r="B4" t="n">
-        <v>79549</v>
+        <v>79555</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,16 +904,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1110,7 +1111,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121061679</v>
+        <v>120551674</v>
       </c>
       <c r="B6" t="n">
         <v>79555</v>
@@ -1144,22 +1145,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grodtjärnsberget, Ång</t>
+          <t>Grodtjärnsberget, Grodtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>625350</v>
+        <v>625335</v>
       </c>
       <c r="R6" t="n">
-        <v>6955478</v>
+        <v>6955500</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1183,12 +1181,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1197,7 +1195,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1216,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120551674</v>
+        <v>121061682</v>
       </c>
       <c r="B7" t="n">
-        <v>79555</v>
+        <v>79682</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1228,41 +1225,44 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>392</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grodtjärnsberget, Grodtjärnsberget, Ång</t>
+          <t>Grodtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>625335</v>
+        <v>625371</v>
       </c>
       <c r="R7" t="n">
-        <v>6955500</v>
+        <v>6955482</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1300,6 +1300,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1415,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121061647</v>
+        <v>121061645</v>
       </c>
       <c r="B9" t="n">
-        <v>98081</v>
+        <v>79549</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1431,27 +1432,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>385</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>

--- a/artfynd/A 8412-2024 artfynd.xlsx
+++ b/artfynd/A 8412-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121061647</v>
+        <v>121061682</v>
       </c>
       <c r="B2" t="n">
-        <v>98081</v>
+        <v>79685</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>625356</v>
+        <v>625371</v>
       </c>
       <c r="R2" t="n">
-        <v>6955527</v>
+        <v>6955482</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,7 +784,7 @@
         <v>121061679</v>
       </c>
       <c r="B3" t="n">
-        <v>79555</v>
+        <v>79558</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -888,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121061671</v>
+        <v>121061683</v>
       </c>
       <c r="B4" t="n">
-        <v>79555</v>
+        <v>98094</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,26 +903,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>392</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>625356</v>
+        <v>625374</v>
       </c>
       <c r="R4" t="n">
-        <v>6955527</v>
+        <v>6955549</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,6 +967,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Uppskattningsvis 6-700 bladrosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120550720</v>
+        <v>120551674</v>
       </c>
       <c r="B5" t="n">
-        <v>79555</v>
+        <v>79558</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>625345</v>
+        <v>625335</v>
       </c>
       <c r="R5" t="n">
-        <v>6955540</v>
+        <v>6955500</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1067,24 +1072,9 @@
           <t>2024-10-22</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Tidigare känt fynd.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120551674</v>
+        <v>120552065</v>
       </c>
       <c r="B6" t="n">
-        <v>79555</v>
+        <v>91400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,25 +1113,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>392</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Aspgelélav</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1151,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>625335</v>
+        <v>625396</v>
       </c>
       <c r="R6" t="n">
-        <v>6955500</v>
+        <v>6955526</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1213,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121061682</v>
+        <v>121061645</v>
       </c>
       <c r="B7" t="n">
-        <v>79682</v>
+        <v>79552</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,25 +1210,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>385</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1256,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>625371</v>
+        <v>625356</v>
       </c>
       <c r="R7" t="n">
-        <v>6955482</v>
+        <v>6955527</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,10 +1304,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120552065</v>
+        <v>121061671</v>
       </c>
       <c r="B8" t="n">
-        <v>91388</v>
+        <v>79558</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,36 +1316,44 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>757</v>
+        <v>392</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Aspgelélav</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grodtjärnsberget, Grodtjärnsberget, Ång</t>
+          <t>Grodtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>625396</v>
+        <v>625356</v>
       </c>
       <c r="R8" t="n">
-        <v>6955526</v>
+        <v>6955527</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1384,12 +1377,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1398,6 +1391,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1416,10 +1410,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121061645</v>
+        <v>121061647</v>
       </c>
       <c r="B9" t="n">
-        <v>79549</v>
+        <v>98094</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1432,26 +1426,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>385</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1522,10 +1517,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121061683</v>
+        <v>120550720</v>
       </c>
       <c r="B10" t="n">
-        <v>98081</v>
+        <v>79558</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1538,41 +1533,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>392</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Grodtjärnsberget, Ång</t>
+          <t>Grodtjärnsberget, Grodtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>625374</v>
+        <v>625345</v>
       </c>
       <c r="R10" t="n">
-        <v>6955549</v>
+        <v>6955540</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1596,17 +1587,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Uppskattningsvis 6-700 bladrosetter</t>
+          <t>Tidigare känt fynd.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1615,7 +1616,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8412-2024 artfynd.xlsx
+++ b/artfynd/A 8412-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121061645</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120550720</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120551674</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1083,6 +1103,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121061671</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121061679</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1281,6 +1311,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120552065</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1382,6 +1417,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121061682</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1484,6 +1524,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121061647</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1591,8 +1636,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121061683</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>